--- a/log.xlsx
+++ b/log.xlsx
@@ -830,27 +830,30 @@
         </is>
       </c>
       <c r="I2" s="29" t="n">
-        <v>4604.09</v>
-      </c>
-      <c r="J2" s="31">
-        <f>IF(OR(I2="",C2=""),"",(I2-C2)/C2)</f>
-        <v/>
-      </c>
-      <c r="K2" s="28">
-        <f>IF(J2="","",IF(J2&gt;0,"涨",IF(J2&lt;0,"跌","平")))</f>
-        <v/>
-      </c>
-      <c r="L2" s="28">
-        <f>IF(J2="","",IF(ABS(J2)&lt;=0.003,"小",IF(ABS(J2)&lt;=0.01,"中","大")))</f>
-        <v/>
-      </c>
-      <c r="M2" s="28">
-        <f>IF(OR(D2="",K2=""),"",IF(D2=K2,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="N2" s="28">
-        <f>IF(OR(E2="",L2=""),"",IF(E2=L2,"√","×"))</f>
-        <v/>
+        <v>4593.200195</v>
+      </c>
+      <c r="J2" s="31" t="n">
+        <v>1.2097</v>
+      </c>
+      <c r="K2" s="28" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="M2" s="28" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="N2" s="28" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
       <c r="O2" s="30" t="inlineStr">
         <is>
@@ -864,7 +867,7 @@
       </c>
       <c r="Q2" s="30" t="inlineStr">
         <is>
-          <t>周六06:30定时结算失败(UTC时区误判+会话无产出)，8/24手动补结算；实际价=周五纽约收盘(新闻源previous close 4604.09，与LBMA周五定盘4582.10及+1.69%单日涨幅互证)</t>
+          <t>周六06:30定时结算失败(UTC时区误判+会话无产出)，8/24手动补结算；实际价=周五纽约收盘(新闻源previous close 4604.09，与LBMA周五定盘4582.10及+1.69%单日涨幅互证)；[2026-08-27 23:15 批量结算] 实际价=$4593.200195, 涨跌=+1.21%</t>
         </is>
       </c>
       <c r="R2" s="24" t="n">
@@ -910,26 +913,31 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I3" s="33" t="n"/>
-      <c r="J3" s="35">
-        <f>IF(OR(I3="",C3=""),"",(I3-C3)/C3)</f>
-        <v/>
-      </c>
-      <c r="K3" s="32">
-        <f>IF(J3="","",IF(J3&gt;0,"涨",IF(J3&lt;0,"跌","平")))</f>
-        <v/>
-      </c>
-      <c r="L3" s="32">
-        <f>IF(J3="","",IF(ABS(J3)&lt;=0.003,"小",IF(ABS(J3)&lt;=0.01,"中","大")))</f>
-        <v/>
-      </c>
-      <c r="M3" s="32">
-        <f>IF(OR(D3="",K3=""),"",IF(D3=K3,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="N3" s="32">
-        <f>IF(OR(E3="",L3=""),"",IF(E3=L3,"√","×"))</f>
-        <v/>
+      <c r="I3" s="33" t="n">
+        <v>4593.200195</v>
+      </c>
+      <c r="J3" s="35" t="n">
+        <v>-1.0918</v>
+      </c>
+      <c r="K3" s="32" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="L3" s="32" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="M3" s="32" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="N3" s="32" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
       <c r="O3" s="34" t="inlineStr">
         <is>
@@ -943,7 +951,7 @@
       </c>
       <c r="Q3" s="34" t="inlineStr">
         <is>
-          <t>周一06:30定时执行失败(UTC时钟周日误判)，10:15手动补跑；基准价为10:15实时价(晚于06:00切点)；口径已改为当日趋势</t>
+          <t>周一06:30定时执行失败(UTC时钟周日误判)，10:15手动补跑；基准价为10:15实时价(晚于06:00切点)；口径已改为当日趋势；[2026-08-27 23:15 批量结算] 实际价=$4593.200195, 涨跌=-1.09%</t>
         </is>
       </c>
       <c r="R3" s="24" t="n">
@@ -1025,7 +1033,7 @@
           <t>[2026-08-27 20:20 自动生成]</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="24" t="n">
         <v>68</v>
       </c>
     </row>
@@ -14555,8 +14563,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="n">
-        <v>0</v>
+      <c r="B2" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="25">
@@ -14575,10 +14583,8 @@
           <t>累计预测行数</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="38" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="25">
@@ -14587,10 +14593,8 @@
           <t>方向正确率（累计）</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="40" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="25">
@@ -14599,10 +14603,8 @@
           <t>档位正确率（累计）</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="41" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="25">
@@ -14611,10 +14613,8 @@
           <t>方向正确率（近30次）</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="40" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="25">
@@ -14623,10 +14623,8 @@
           <t>档位正确率（近30次）</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="41" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
@@ -14658,7 +14656,7 @@
           <t>注：尚无已结算预测时显示 "-" 属正常；数据填入后自动更新。</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14669,7 +14667,7 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="25">

--- a/log.xlsx
+++ b/log.xlsx
@@ -997,26 +997,31 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I4" s="29" t="n"/>
-      <c r="J4" s="31">
-        <f>IF(OR(I4="",C4=""),"",(I4-C4)/C4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="28">
-        <f>IF(J4="","",IF(J4&gt;0,"涨",IF(J4&lt;0,"跌","平")))</f>
-        <v/>
-      </c>
-      <c r="L4" s="28">
-        <f>IF(J4="","",IF(ABS(J4)&lt;=0.003,"小",IF(ABS(J4)&lt;=0.01,"中","大")))</f>
-        <v/>
-      </c>
-      <c r="M4" s="28">
-        <f>IF(OR(D4="",K4=""),"",IF(D4=K4,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="N4" s="28">
-        <f>IF(OR(E4="",L4=""),"",IF(E4=L4,"√","×"))</f>
-        <v/>
+      <c r="I4" s="29" t="n">
+        <v>4612</v>
+      </c>
+      <c r="J4" s="31" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="K4" s="28" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M4" s="28" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="N4" s="28" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
       <c r="O4" s="28" t="inlineStr">
         <is>
@@ -1030,7 +1035,7 @@
       </c>
       <c r="Q4" s="28" t="inlineStr">
         <is>
-          <t>[2026-08-27 20:20 自动生成]</t>
+          <t>[2026-08-27 20:20 自动生成]；[2026-08-28 00:02 批量结算] 实际价=$4612.0, 涨跌=+0.36%</t>
         </is>
       </c>
       <c r="R4" s="24" t="n">
@@ -1038,14 +1043,44 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="25">
-      <c r="A5" s="32" t="n"/>
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:02</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>4612</v>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="I5" s="33" t="n"/>
       <c r="J5" s="35">
         <f>IF(OR(I5="",C5=""),"",(I5-C5)/C5)</f>
@@ -1067,9 +1102,24 @@
         <f>IF(OR(E5="",L5=""),"",IF(E5=L5,"√","×"))</f>
         <v/>
       </c>
-      <c r="O5" s="32" t="n"/>
-      <c r="P5" s="32" t="n"/>
-      <c r="Q5" s="32" t="n"/>
+      <c r="O5" s="32" t="inlineStr">
+        <is>
+          <t>趋势涨</t>
+        </is>
+      </c>
+      <c r="P5" s="32" t="inlineStr">
+        <is>
+          <t>利多因素：短期上升趋势、人民币买盘支撑、超跌反弹需求。利空因素：VIX低位、获利回吐、技术阻力、美元走强。综合来看，利空略占上风，预计今日小幅下跌。</t>
+        </is>
+      </c>
+      <c r="Q5" s="32" t="inlineStr">
+        <is>
+          <t>[2026-08-28 00:02 自动生成]</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="25">
       <c r="A6" s="28" t="n"/>
@@ -14564,7 +14614,7 @@
     </row>
     <row r="2">
       <c r="B2" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="25">
@@ -14574,7 +14624,7 @@
         </is>
       </c>
       <c r="B3" s="38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="25">
@@ -14584,7 +14634,7 @@
         </is>
       </c>
       <c r="B4" s="38" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="25">
@@ -14604,7 +14654,7 @@
         </is>
       </c>
       <c r="B6" s="41" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="25">
@@ -14624,7 +14674,7 @@
         </is>
       </c>
       <c r="B8" s="41" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
@@ -14657,7 +14707,7 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="25">
@@ -14667,7 +14717,7 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="25">

--- a/log.xlsx
+++ b/log.xlsx
@@ -1081,26 +1081,31 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I5" s="33" t="n"/>
-      <c r="J5" s="35">
-        <f>IF(OR(I5="",C5=""),"",(I5-C5)/C5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="32">
-        <f>IF(J5="","",IF(J5&gt;0,"涨",IF(J5&lt;0,"跌","平")))</f>
-        <v/>
-      </c>
-      <c r="L5" s="32">
-        <f>IF(J5="","",IF(ABS(J5)&lt;=0.003,"小",IF(ABS(J5)&lt;=0.01,"中","大")))</f>
-        <v/>
-      </c>
-      <c r="M5" s="32">
-        <f>IF(OR(D5="",K5=""),"",IF(D5=K5,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="N5" s="32">
-        <f>IF(OR(E5="",L5=""),"",IF(E5=L5,"√","×"))</f>
-        <v/>
+      <c r="I5" s="33" t="n">
+        <v>4456.399902</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <v>-3.3738</v>
+      </c>
+      <c r="K5" s="32" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="L5" s="32" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="M5" s="32" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
       </c>
       <c r="O5" s="32" t="inlineStr">
         <is>
@@ -1114,10 +1119,10 @@
       </c>
       <c r="Q5" s="32" t="inlineStr">
         <is>
-          <t>[2026-08-28 00:02 自动生成]</t>
+          <t>[2026-08-28 00:02 自动生成]；[2026-08-29 05:51 批量结算] 实际价=$4456.399902, 涨跌=-3.37%</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="24" t="n">
         <v>60</v>
       </c>
     </row>
@@ -14614,7 +14619,7 @@
     </row>
     <row r="2">
       <c r="B2" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="25">
@@ -14634,7 +14639,7 @@
         </is>
       </c>
       <c r="B4" s="38" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="25">
@@ -14644,7 +14649,7 @@
         </is>
       </c>
       <c r="B5" s="40" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="25">
@@ -14654,7 +14659,7 @@
         </is>
       </c>
       <c r="B6" s="41" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="25">
@@ -14664,7 +14669,7 @@
         </is>
       </c>
       <c r="B7" s="40" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="25">
@@ -14674,7 +14679,7 @@
         </is>
       </c>
       <c r="B8" s="41" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
@@ -14717,7 +14722,7 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="25">
